--- a/imports/docs/employees.xlsx
+++ b/imports/docs/employees.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="employees" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Funcionários" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,23 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00138D83"/>
+        <bgColor rgb="00138D83"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,198 +426,212 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>registry</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>birth_date</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>department_id</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>position</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>department_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EMP001</t>
+          <t>FUNC00001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carlos Souza</t>
+          <t>Beatriz Costa Vieira</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10/06/1985</t>
+          <t>12/08/1977</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>carlos.souza@escola.com</t>
+          <t>beatriz.vieiraFUNC00001@escola.edu.br</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Professor</t>
+          <t>PEDAGOGIA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Pedagoga</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EMP002</t>
+          <t>FUNC00002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lucia Santos</t>
+          <t>Marcos Araújo Cunha</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25/09/1990</t>
+          <t>28/10/1986</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>lucia.santos@escola.com</t>
+          <t>marcos.cunhaFUNC00002@escola.edu.br</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coordenadora</t>
+          <t>PEDAGOGIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>Pedagoga</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EMP003</t>
+          <t>FUNC00003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fernanda Lima</t>
+          <t>Fernando Azevedo Guimarães</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>03/12/1978</t>
+          <t>27/07/1989</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>fernanda.lima@escola.com</t>
+          <t>fernando.guimaraesFUNC00003@escola.edu.br</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diretora</t>
+          <t>PEDAGOGIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>Coordenador Pedagógico</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EMP004</t>
+          <t>FUNC00004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Roberto Alves</t>
+          <t>Natália Moura Carvalho</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17/04/1982</t>
+          <t>24/12/1983</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>natalia.carvalhoFUNC00004@escola.edu.br</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auxiliar de Servicos</t>
+          <t>PEDAGOGIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>Psicóloga Escolar</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EMP005</t>
+          <t>FUNC00005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marcia Oliveira</t>
+          <t>Manuela Ribeiro Martins</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -614,17 +641,7237 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08/08/1995</t>
+          <t>16/10/1975</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>marcia.o@escola.com</t>
+          <t>manuela.martinsFUNC00005@escola.edu.br</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Secretaria</t>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Psicóloga Escolar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FUNC00006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Maria Barbosa Lopes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>02/09/1978</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>maria.lopesFUNC00006@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Psicóloga Escolar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FUNC00007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Thiago Nascimento Cunha</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>27/03/1975</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>thiago.cunhaFUNC00007@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Psicóloga Escolar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FUNC00008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bruna Machado Pereira</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>18/02/1979</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>bruna.pereiraFUNC00008@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Orientador Educacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FUNC00009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Henrique Rezende Nascimento</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>09/09/1967</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>henrique.nascimentoFUNC00009@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Orientador Educacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FUNC00010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Patrícia Pinto Cavalcante</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>02/12/1971</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>patricia.cavalcanteFUNC00010@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pedagoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FUNC00011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Laís Pereira Alves</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>02/09/1971</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>lais.alvesFUNC00011@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Psicóloga Escolar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FUNC00012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bruno Carvalho Andrade</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>10/12/1975</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>bruno.andradeFUNC00012@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pedagoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FUNC00013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Maria Azevedo Alves</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>12/11/1974</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>maria.alvesFUNC00013@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Coordenador Pedagógico</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FUNC00014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Lívia Martins Mendes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>08/01/1991</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>livia.mendesFUNC00014@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pedagoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FUNC00015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Danilo Costa Ferreira</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>23/06/1982</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>danilo.ferreiraFUNC00015@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pedagoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FUNC00016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kaique Lopes Gomes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>26/07/1998</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>kaique.gomesFUNC00016@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Orientador Educacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FUNC00017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Vitor Marques Marques</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>26/09/1994</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vitor.marquesFUNC00017@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PEDAGOGIA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Coordenador Pedagógico</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FUNC00018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Joana Gomes Brito</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>26/12/1965</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>joana.britoFUNC00018@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Monitor Pedagógico</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FUNC00019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Larissa Dias Rocha</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>14/03/1990</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>larissa.rochaFUNC00019@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FUNC00020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lucas Cavalcante Borges</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>02/10/1974</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>lucas.borgesFUNC00020@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Monitor Pedagógico</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FUNC00021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Isadora Santana Vieira</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>22/07/1991</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>isadora.vieiraFUNC00021@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Monitor Pedagógico</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FUNC00022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Yasmin Azevedo Duarte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>01/06/1985</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>yasmin.duarteFUNC00022@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FUNC00023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bárbara Gomes Monteiro</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>21/08/1990</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>barbara.monteiroFUNC00023@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FUNC00024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bárbara Rezende Moura</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>12/12/1993</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>barbara.mouraFUNC00024@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Monitor Pedagógico</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FUNC00025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>André Barbosa Ferreira</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>11/09/1967</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>andre.ferreiraFUNC00025@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FUNC00026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Clarice Lima Santana</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>07/05/1999</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>clarice.santanaFUNC00026@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FUNC00027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Yasmin Santana Dias</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>01/01/1975</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>yasmin.diasFUNC00027@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Monitor Pedagógico</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FUNC00028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sabrina Brito Barbosa</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>04/09/1992</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>sabrina.barbosaFUNC00028@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Monitor Pedagógico</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FUNC00029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Alexandre Sousa Correia</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>04/06/1997</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>alexandre.correiaFUNC00029@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FUNC00030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Lívia Mendes Barbosa</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>11/08/1965</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>livia.barbosaFUNC00030@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FUNC00031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Viviane Campos Guimarães</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>08/10/1999</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>viviane.guimaraesFUNC00031@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FUNC00032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kaique Rezende Xavier</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>13/12/1973</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>kaique.xavierFUNC00032@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Monitor Pedagógico</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FUNC00033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Letícia Rocha Santana</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>15/06/1977</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>leticia.santanaFUNC00033@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FUNC00034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Vitor Marques Ferreira</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>14/01/1970</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>vitor.ferreiraFUNC00034@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>COORD_EF1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FUNC00035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Leandro Rodrigues Andrade</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>19/07/1998</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>leandro.andradeFUNC00035@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Monitor Pedagógico</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FUNC00036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Elisa Sousa Araújo</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>14/11/1996</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>elisa.araujoFUNC00036@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FUNC00037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Maria Azevedo Marques</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>17/03/1975</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>maria.marquesFUNC00037@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FUNC00038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Renato Lima Guimarães</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>04/09/1997</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>renato.guimaraesFUNC00038@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Monitor Pedagógico</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FUNC00039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sérgio Oliveira Duarte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>12/09/1975</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>sergio.duarteFUNC00039@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FUNC00040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Gabriela Pereira Pereira</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10/10/1988</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>gabriela.pereiraFUNC00040@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FUNC00041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Lívia Andrade Barbosa</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10/05/1988</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>livia.barbosaFUNC00041@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FUNC00042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rodrigo Gomes Rezende</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>10/01/1991</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>rodrigo.rezendeFUNC00042@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FUNC00043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nicolás Ramos Silva</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>12/09/1972</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>nicolas.silvaFUNC00043@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FUNC00044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Gabriela Cardoso Campos</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>15/10/1984</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>gabriela.camposFUNC00044@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FUNC00045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Luana Azevedo Pinto</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>17/03/1973</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>luana.pintoFUNC00045@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Monitor Pedagógico</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>FUNC00046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Leandro Cavalcante Mendes</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>11/12/1974</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>leandro.mendesFUNC00046@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>FUNC00047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Isadora Moura Marques</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>13/04/1989</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>isadora.marquesFUNC00047@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FUNC00048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Isadora Mendes Duarte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>03/11/1982</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>isadora.duarteFUNC00048@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>FUNC00049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Thaís Correia Rezende</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>21/09/1984</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>thais.rezendeFUNC00049@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FUNC00050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Larissa Martins Moura</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>25/10/1999</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>larissa.mouraFUNC00050@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>FUNC00051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Renata Martins Melo</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>01/09/1995</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>renata.meloFUNC00051@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>COORD_EF2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>FUNC00052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sandra Ribeiro Santos</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>08/04/1982</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>sandra.santosFUNC00052@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tutor Acadêmico</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>FUNC00053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Viviane Mendes Ferreira</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>11/10/1999</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>viviane.ferreiraFUNC00053@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FUNC00054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Maria Santos Dias</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>14/03/1992</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>maria.diasFUNC00054@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>FUNC00055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Amanda Moreira Sousa</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>04/02/1970</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>amanda.sousaFUNC00055@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tutor Acadêmico</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FUNC00056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Rodrigo Ribeiro Sousa</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>10/03/1970</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>rodrigo.sousaFUNC00056@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>FUNC00057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Fernanda Moura Rocha</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>23/01/1976</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>fernanda.rochaFUNC00057@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>FUNC00058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Rafael Rocha Gomes</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>09/06/1991</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>rafael.gomesFUNC00058@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>FUNC00059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Lívia Souza Martins</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>19/10/1980</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>livia.martinsFUNC00059@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>FUNC00060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Yago Gonçalves Moreira</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>02/05/1972</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>yago.moreiraFUNC00060@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>FUNC00061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Igor Rodrigues Cardoso</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>21/07/1966</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>igor.cardosoFUNC00061@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Coordenador de Área</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>FUNC00062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Beatriz Fernandes Castro</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>25/04/1971</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>beatriz.castroFUNC00062@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tutor Acadêmico</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FUNC00063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Manuela Barbosa Campos</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>03/08/1991</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>manuela.camposFUNC00063@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tutor Acadêmico</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FUNC00064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Mariana Andrade Teixeira</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>18/04/1975</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>mariana.teixeiraFUNC00064@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FUNC00065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tatiana Mendes Oliveira</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>27/08/1965</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>tatiana.oliveiraFUNC00065@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tutor Acadêmico</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>FUNC00066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Daniel Silva Souza</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>20/05/1995</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>daniel.souzaFUNC00066@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>FUNC00067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Débora Nascimento Correia</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>27/10/1978</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>debora.correiaFUNC00067@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tutor Acadêmico</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>FUNC00068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Daniel Duarte Teixeira</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>03/05/1969</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>daniel.teixeiraFUNC00068@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>COORD_EM</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Professor Assistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>FUNC00069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Manuela Azevedo Castro</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>07/07/1982</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>manuela.castroFUNC00069@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Atendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>FUNC00070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Amanda Cunha Dias</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>15/12/1981</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>amanda.diasFUNC00070@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Auxiliar Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>FUNC00071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Victor Dias Carvalho</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>11/10/1994</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>victor.carvalhoFUNC00071@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Secretário Escolar</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FUNC00072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Manuela Borges Silva</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>01/01/1995</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>manuela.silvaFUNC00072@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Atendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FUNC00073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Luiz Monteiro Guimarães</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>18/07/1996</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>luiz.guimaraesFUNC00073@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Secretário Escolar</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FUNC00074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Valentina Borges Rodrigues</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>27/01/1999</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>valentina.rodriguesFUNC00074@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Atendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FUNC00075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Bruno Nascimento Xavier</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>12/10/1989</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>bruno.xavierFUNC00075@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Auxiliar Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FUNC00076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Samuel Farias Monteiro</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>15/02/1965</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>samuel.monteiroFUNC00076@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Auxiliar Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FUNC00077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Joana Silva Almeida</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>22/05/1966</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>joana.almeidaFUNC00077@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Atendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>FUNC00078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Felipe Xavier Moura</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>08/12/1984</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>felipe.mouraFUNC00078@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Secretário Escolar</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>FUNC00079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Daniela Oliveira Fernandes</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>23/12/1996</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>daniela.fernandesFUNC00079@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Atendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FUNC00080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>André Xavier Correia</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>28/02/1990</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>andre.correiaFUNC00080@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Auxiliar Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>FUNC00081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Maria Costa Castro</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>24/11/1977</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>maria.castroFUNC00081@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Atendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FUNC00082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Aline Campos Ribeiro</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>05/10/1969</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>aline.ribeiroFUNC00082@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Atendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>FUNC00083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Thiago Campos Almeida</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>26/12/1998</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>thiago.almeidaFUNC00083@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Auxiliar Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>FUNC00084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Cauã Santos Monteiro</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>09/10/1999</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>caua.monteiroFUNC00084@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Atendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>FUNC00085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Laura Silva Machado</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>14/06/1968</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>laura.machadoFUNC00085@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SECRETARIA</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Auxiliar Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>FUNC00086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Cauã Santana Freitas</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>17/06/1996</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>caua.freitasFUNC00086@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Gerente Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>FUNC00087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Raquel Souza Fernandes</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>15/09/1991</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>raquel.fernandesFUNC00087@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Recepcionista</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>FUNC00088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>André Dias Ferreira</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>08/12/1966</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>andre.ferreiraFUNC00088@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Assistente Executivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>FUNC00089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Sabrina Martins Costa</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>03/05/1986</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>sabrina.costaFUNC00089@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Gerente Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FUNC00090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Vitor Farias Santos</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>08/05/1986</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>vitor.santosFUNC00090@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Gerente Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>FUNC00091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Henrique Souza Xavier</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>26/09/1986</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>henrique.xavierFUNC00091@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Auxiliar Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>FUNC00092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Nathalia Pinto Moura</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>21/02/1993</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>nathalia.mouraFUNC00092@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Assistente Executivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>FUNC00093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Larissa Souza Oliveira</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>28/06/1989</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>larissa.oliveiraFUNC00093@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Gerente Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>FUNC00094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Fernanda Farias Mendes</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>20/05/1968</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>fernanda.mendesFUNC00094@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Assistente Executivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>FUNC00095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Cauã Souza Castro</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>28/05/1968</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>caua.castroFUNC00095@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Assistente Executivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FUNC00096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Jorge Melo Marques</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>26/10/1979</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>jorge.marquesFUNC00096@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Gerente Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>FUNC00097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Renato Rezende Machado</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>21/06/1971</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>renato.machadoFUNC00097@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Gerente Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>FUNC00098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Henrique Araújo Martins</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>01/02/1971</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>henrique.martinsFUNC00098@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Gerente Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>FUNC00099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Priscila Campos Lima</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>12/05/1997</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>priscila.limaFUNC00099@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Assistente Executivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FUNC00100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Jorge Mendes Ribeiro</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>26/03/1980</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>jorge.ribeiroFUNC00100@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Gerente Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>FUNC00101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Diego Araújo Machado</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>25/11/1997</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>diego.machadoFUNC00101@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Recepcionista</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FUNC00102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Guilherme Brito Gomes</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>10/08/1974</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>guilherme.gomesFUNC00102@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Recepcionista</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>FUNC00103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>João Santana Araújo</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>08/01/1974</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>joao.araujoFUNC00103@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Técnico de Folha de Pagamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FUNC00104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Tatiana Souza Machado</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>07/04/1987</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>tatiana.machadoFUNC00104@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Técnico de Folha de Pagamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FUNC00105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Juliana Dias Martins</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>23/12/1995</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>juliana.martinsFUNC00105@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Assistente de RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>FUNC00106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Bruna Araújo Campos</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>10/10/1986</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>bruna.camposFUNC00106@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Assistente de RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>FUNC00107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Rafael Freitas Rezende</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>08/08/1967</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>rafael.rezendeFUNC00107@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Analista de RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>FUNC00108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Giovanna Almeida Freitas</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>16/04/1978</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>giovanna.freitasFUNC00108@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Técnico de Folha de Pagamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>FUNC00109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Bruna Farias Duarte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>13/04/1989</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>bruna.duarteFUNC00109@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Analista de RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>FUNC00110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Ana Andrade Silva</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>01/06/1969</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>ana.silvaFUNC00110@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Técnico de Folha de Pagamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>FUNC00111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Fernando Mendes Martins</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>01/01/1988</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>fernando.martinsFUNC00111@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Analista de RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>FUNC00112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Eduardo Almeida Sousa</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>28/06/1976</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>eduardo.sousaFUNC00112@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Técnico de Folha de Pagamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FUNC00113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>André Santos Ribeiro</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>01/02/1981</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>andre.ribeiroFUNC00113@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Técnico de Folha de Pagamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>FUNC00114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Ruan Rezende Pereira</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>10/04/1986</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ruan.pereiraFUNC00114@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Assistente de RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>FUNC00115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Alexandre Cavalcante Costa</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>14/10/1998</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>alexandre.costaFUNC00115@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Técnico de Folha de Pagamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>FUNC00116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Rodrigo Lima Rezende</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>18/04/1977</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>rodrigo.rezendeFUNC00116@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Assistente de RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>FUNC00117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Amanda Pinto Machado</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>25/01/1980</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>amanda.machadoFUNC00117@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Técnico de Folha de Pagamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>FUNC00118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Sandra Vieira Rezende</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>08/06/1974</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>sandra.rezendeFUNC00118@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Analista de RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>FUNC00119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Vanessa Lima Gonçalves</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>24/04/1996</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>vanessa.goncalvesFUNC00119@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Analista de RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>FUNC00120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Isadora Moura Rodrigues</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>13/09/1975</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>isadora.rodriguesFUNC00120@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Desenvolvedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>FUNC00121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Renato Ribeiro Rocha</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>23/09/1988</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>renato.rochaFUNC00121@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Técnico em Informática</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>FUNC00122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Maria Cardoso Fernandes</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>26/11/1990</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>maria.fernandesFUNC00122@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Analista de TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>FUNC00123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>André Mendes Lopes</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>10/04/1990</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>andre.lopesFUNC00123@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Técnico em Informática</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>FUNC00124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Thaís Costa Andrade</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>03/09/1981</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>thais.andradeFUNC00124@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Suporte Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>FUNC00125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Vitória Mendes Santana</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>19/04/1987</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>vitoria.santanaFUNC00125@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Analista de TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>FUNC00126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Jorge Dias Machado</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>14/08/1993</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>jorge.machadoFUNC00126@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Técnico em Informática</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>FUNC00127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Fábio Rocha Fernandes</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>06/01/1989</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>fabio.fernandesFUNC00127@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Técnico em Informática</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>FUNC00128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ruan Rodrigues Nascimento</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>27/05/1970</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>ruan.nascimentoFUNC00128@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Analista de TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>FUNC00129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Raquel Alves Pereira</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>02/06/1969</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>raquel.pereiraFUNC00129@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Suporte Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>FUNC00130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Cauã Dias Sousa</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>27/12/1984</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>caua.sousaFUNC00130@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Desenvolvedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>FUNC00131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Francisco Lima Melo</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>01/05/1999</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>francisco.meloFUNC00131@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Desenvolvedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>FUNC00132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Ricardo Rezende Nunes</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>25/10/1990</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>ricardo.nunesFUNC00132@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Analista de TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>FUNC00133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Danilo Melo Gomes</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>08/04/1990</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>danilo.gomesFUNC00133@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Suporte Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>FUNC00134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Tiago Araújo Rezende</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>24/08/2000</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>tiago.rezendeFUNC00134@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Técnico em Informática</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>FUNC00135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Felipe Rocha Martins</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>14/12/1992</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>felipe.martinsFUNC00135@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Suporte Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>FUNC00136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Luiz Santos Andrade</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>28/10/1973</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>luiz.andradeFUNC00136@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Suporte Técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>FUNC00137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Nicolás Silva Ramos</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>08/06/1987</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>nicolas.ramosFUNC00137@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Encanador</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>FUNC00138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Yago Nunes Melo</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>11/05/1999</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>yago.meloFUNC00138@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Técnico de Manutenção</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>FUNC00139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Camila Lima Gomes</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>21/10/1986</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>camila.gomesFUNC00139@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Encanador</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>FUNC00140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Rafaela Nunes Rodrigues</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>07/07/1999</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>rafaela.rodriguesFUNC00140@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Encanador</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>FUNC00141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Antônio Mendes Correia</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>06/02/1984</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>antonio.correiaFUNC00141@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Técnico de Manutenção</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>FUNC00142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Paula Oliveira Xavier</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>06/01/1996</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>paula.xavierFUNC00142@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Auxiliar de Manutenção</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FUNC00143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Marcelo Vieira Carvalho</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>22/05/1979</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>marcelo.carvalhoFUNC00143@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Técnico de Manutenção</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>FUNC00144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Alexandre Santana Silva</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>28/06/1975</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>alexandre.silvaFUNC00144@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Encanador</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>FUNC00145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Bruno Lima Teixeira</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>24/08/1991</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>bruno.teixeiraFUNC00145@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Técnico de Manutenção</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>FUNC00146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Carlos Lima Carvalho</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>27/07/1984</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>carlos.carvalhoFUNC00146@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Encanador</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>FUNC00147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Antônio Barbosa Araújo</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>23/09/1977</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>antonio.araujoFUNC00147@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Encanador</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>FUNC00148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>João Gomes Mendes</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>20/07/1969</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>joao.mendesFUNC00148@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Auxiliar de Manutenção</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>FUNC00149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Thaís Ramos Freitas</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>02/10/1994</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>thais.freitasFUNC00149@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Técnico de Manutenção</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>FUNC00150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Renato Nascimento Monteiro</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>20/07/1984</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>renato.monteiroFUNC00150@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Auxiliar de Manutenção</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>FUNC00151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Eduardo Moura Azevedo</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>13/08/1992</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>eduardo.azevedoFUNC00151@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Auxiliar de Manutenção</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>FUNC00152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Letícia Nunes Monteiro</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>28/04/1967</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>leticia.monteiroFUNC00152@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>MANUT</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Auxiliar de Manutenção</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>FUNC00153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Roberto Teixeira Vieira</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>24/12/1969</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>roberto.vieiraFUNC00153@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Assistente de Acervo</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>FUNC00154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Maria Marques Melo</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>12/02/2000</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>maria.meloFUNC00154@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Bibliotecário</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>FUNC00155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Patrícia Brito Brito</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>15/07/1985</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>patricia.britoFUNC00155@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Bibliotecário</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>FUNC00156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Danilo Oliveira Freitas</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>21/02/1966</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>danilo.freitasFUNC00156@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Assistente de Acervo</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>FUNC00157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Laura Moreira Dias</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>13/04/1990</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>laura.diasFUNC00157@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Bibliotecário</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>FUNC00158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Bruno Guimarães Lima</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>24/11/1985</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>bruno.limaFUNC00158@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Auxiliar de Biblioteca</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>FUNC00159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Matheus Ferreira Castro</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>15/12/1980</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>matheus.castroFUNC00159@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Bibliotecário</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>FUNC00160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Leonardo Costa Costa</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>04/10/1966</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>leonardo.costaFUNC00160@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Bibliotecário</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>FUNC00161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Guilherme Duarte Nunes</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>22/02/1975</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>guilherme.nunesFUNC00161@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Bibliotecário</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>FUNC00162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Mariana Mendes Nascimento</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>23/04/1976</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>mariana.nascimentoFUNC00162@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Bibliotecário</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>FUNC00163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Sandra Carvalho Mendes</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>26/11/1968</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>sandra.mendesFUNC00163@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Assistente de Acervo</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>FUNC00164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Eduarda Cavalcante Alves</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>10/12/1989</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>eduarda.alvesFUNC00164@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Auxiliar de Biblioteca</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>FUNC00165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>João Souza Brito</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>08/04/1989</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>joao.britoFUNC00165@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Auxiliar de Biblioteca</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>FUNC00166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Priscila Ferreira Santos</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>01/01/1991</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>priscila.santosFUNC00166@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Auxiliar de Biblioteca</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>FUNC00167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Alice Cavalcante Rodrigues</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>26/02/1979</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>alice.rodriguesFUNC00167@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Assistente de Acervo</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>FUNC00168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Daniel Oliveira Marques</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>27/02/1997</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>daniel.marquesFUNC00168@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>BIBLIO</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Auxiliar de Biblioteca</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>FUNC00169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Roberto Martins Moura</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>13/09/1978</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>roberto.mouraFUNC00169@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Tesoureiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>FUNC00170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Carlos Alves Nascimento</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>01/03/1985</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>carlos.nascimentoFUNC00170@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Tesoureiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>FUNC00171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Ana Moreira Carvalho</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>03/04/1994</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>ana.carvalhoFUNC00171@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Auxiliar Financeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>FUNC00172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Daniela Oliveira Rodrigues</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>10/07/1978</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>daniela.rodriguesFUNC00172@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Tesoureiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>FUNC00173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Letícia Guimarães Teixeira</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>04/05/1975</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>leticia.teixeiraFUNC00173@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Auxiliar Financeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>FUNC00174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Giovanna Moreira Cunha</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>06/06/1973</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>giovanna.cunhaFUNC00174@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Auxiliar Financeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>FUNC00175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Isadora Cardoso Rodrigues</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>20/01/1986</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>isadora.rodriguesFUNC00175@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Tesoureiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>FUNC00176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Roberto Duarte Almeida</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>23/10/1997</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>roberto.almeidaFUNC00176@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Contador</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>FUNC00177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Jorge Melo Pereira</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>24/04/1984</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>jorge.pereiraFUNC00177@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Tesoureiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>FUNC00178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Bárbara Ferreira Souza</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>16/06/1973</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>barbara.souzaFUNC00178@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Auxiliar Financeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>FUNC00179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Marcelo Carvalho Borges</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>24/04/1967</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>marcelo.borgesFUNC00179@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Tesoureiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>FUNC00180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Bruna Lima Fernandes</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>26/11/1985</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>bruna.fernandesFUNC00180@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Contador</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>FUNC00181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Gabriela Borges Xavier</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>08/01/1983</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>gabriela.xavierFUNC00181@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Auxiliar Financeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>FUNC00182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Carlos Teixeira Souza</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>23/11/1980</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>carlos.souzaFUNC00182@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Analista Financeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>FUNC00183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Débora Santana Rocha</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>21/08/1976</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>debora.rochaFUNC00183@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Contador</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>FUNC00184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Fábio Rodrigues Martins</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>05/11/1968</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>fabio.martinsFUNC00184@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>FINANCEIRO</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Analista Financeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>FUNC00185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Eduardo Araújo Castro</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>17/04/1978</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>eduardo.castroFUNC00185@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Auxiliar de Limpeza</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>FUNC00186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Renato Barbosa Costa</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>14/04/1977</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>renato.costaFUNC00186@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Auxiliar de Limpeza</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>FUNC00187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Yasmin Vieira Campos</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>07/11/1993</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>yasmin.camposFUNC00187@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Zelador</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>FUNC00188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Luana Ferreira Andrade</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>06/07/1990</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>luana.andradeFUNC00188@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Zelador</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>FUNC00189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Danilo Moura Duarte</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>27/03/1992</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>danilo.duarteFUNC00189@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Zelador</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>FUNC00190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Marcelo Machado Ferreira</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>18/10/1984</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>marcelo.ferreiraFUNC00190@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Auxiliar de Limpeza</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>FUNC00191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Paula Sousa Moreira</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>15/05/1994</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>paula.moreiraFUNC00191@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Zelador</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>FUNC00192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Francisco Cardoso Rodrigues</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>23/03/1986</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>francisco.rodriguesFUNC00192@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Zelador</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>FUNC00193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>André Silva Silva</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>24/12/1997</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>andre.silvaFUNC00193@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Zelador</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>FUNC00194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Igor Nunes Duarte</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>16/07/1988</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>igor.duarteFUNC00194@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Zelador</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>FUNC00195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Viviane Rodrigues Marques</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>13/02/1967</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>viviane.marquesFUNC00195@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Faxineiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>FUNC00196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Yago Machado Sousa</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>23/09/1987</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>yago.sousaFUNC00196@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Zelador</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>FUNC00197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Daniela Monteiro Souza</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>24/07/1989</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>daniela.souzaFUNC00197@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Auxiliar de Limpeza</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>FUNC00198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Lucas Xavier Andrade</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>22/12/1966</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>lucas.andradeFUNC00198@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Faxineiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>FUNC00199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Francisco Freitas Cunha</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>08/05/1974</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>francisco.cunhaFUNC00199@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Faxineiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>FUNC00200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Isadora Costa Silva</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>21/02/1972</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>isadora.silvaFUNC00200@escola.edu.br</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>LIMPEZA</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Faxineiro</t>
         </is>
       </c>
     </row>
